--- a/inst/extdata/exampleARS_3.xlsx
+++ b/inst/extdata/exampleARS_3.xlsx
@@ -1,50 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clymb-my.sharepoint.com/personal/mbosman_clymb_onmicrosoft_com/Documents/Documents/siera/inst/extdata/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="11_E75126E222C69DF390F1E656046825349E65D396" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D637438C-FC4A-4803-9396-90597DB66C00}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="StudyInfo" sheetId="2" r:id="rId2"/>
-    <sheet name="ReportingEvent" sheetId="3" r:id="rId3"/>
-    <sheet name="ReferenceDocuments" sheetId="4" r:id="rId4"/>
-    <sheet name="Categorizations" sheetId="5" r:id="rId5"/>
-    <sheet name="MainListOfContents" sheetId="6" r:id="rId6"/>
-    <sheet name="OtherListsOfContents" sheetId="7" r:id="rId7"/>
-    <sheet name="GlobalDisplaySections" sheetId="8" r:id="rId8"/>
-    <sheet name="Outputs" sheetId="9" r:id="rId9"/>
-    <sheet name="OutputProgrammingCode" sheetId="10" r:id="rId10"/>
-    <sheet name="Displays" sheetId="11" r:id="rId11"/>
-    <sheet name="OutputCodeParameters" sheetId="12" r:id="rId12"/>
-    <sheet name="OutputDocumentRefs" sheetId="13" r:id="rId13"/>
-    <sheet name="DataSubsets" sheetId="14" r:id="rId14"/>
-    <sheet name="AnalysisGroupings" sheetId="16" r:id="rId15"/>
-    <sheet name="Analyses" sheetId="17" r:id="rId16"/>
-    <sheet name="AnalysisSets" sheetId="15" r:id="rId17"/>
-    <sheet name="AnalysisProgrammingCode" sheetId="18" r:id="rId18"/>
-    <sheet name="AnalysisCodeParameters" sheetId="19" r:id="rId19"/>
-    <sheet name="AnalysisDocumentRefs" sheetId="20" r:id="rId20"/>
-    <sheet name="AnalysisMethods" sheetId="21" r:id="rId21"/>
-    <sheet name="AnalysisMethodCodeTemplate" sheetId="22" r:id="rId22"/>
-    <sheet name="AnalysisMethodCodeParameters" sheetId="23" r:id="rId23"/>
-    <sheet name="AnalysisMethodDocumentRefs" sheetId="24" r:id="rId24"/>
-    <sheet name="TerminologyExtensions" sheetId="25" r:id="rId25"/>
+    <sheet name="About" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="StudyInfo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ReportingEvent" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ReferenceDocuments" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Categorizations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MainListOfContents" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="OtherListsOfContents" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="GlobalDisplaySections" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Outputs" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="OutputProgrammingCode" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Displays" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="OutputCodeParameters" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="OutputDocumentRefs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="DataSubsets" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="AnalysisGroupings" sheetId="16" state="visible" r:id="rId15"/>
+    <sheet name="Analyses" sheetId="17" state="visible" r:id="rId16"/>
+    <sheet name="AnalysisSets" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="AnalysisProgrammingCode" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="AnalysisCodeParameters" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="AnalysisDocumentRefs" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="AnalysisMethods" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="AnalysisMethodCodeTemplate" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="AnalysisMethodCodeParameters" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="AnalysisMethodDocumentRefs" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="TerminologyExtensions" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="619">
   <si>
     <t>generatedUsing</t>
   </si>
@@ -1950,12 +1943,22 @@
                                                 stat_name == 'min' ~ 'Mth_03_07_Min',
                                                 stat_name == 'max' ~ 'Mth_03_08_Max'))</t>
   </si>
+  <si>
+    <t xml:space="preserve">Mth_02_02_%_NUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mth_02_02_%_DEN</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1964,18 +1967,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b/>
     </font>
     <font>
-      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <strike/>
     </font>
   </fonts>
   <fills count="4">
@@ -2019,7 +2028,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -2030,9 +2038,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2334,11 +2342,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2349,7 +2357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2362,15 +2370,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
@@ -2386,15 +2395,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -2420,14 +2430,14 @@
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>129</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="s">
@@ -2436,7 +2446,7 @@
       <c r="E2" t="s">
         <v>116</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="s">
@@ -2446,14 +2456,14 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>129</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="s">
@@ -2462,7 +2472,7 @@
       <c r="E3" t="s">
         <v>116</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="s">
@@ -2472,14 +2482,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>129</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="s">
@@ -2488,7 +2498,7 @@
       <c r="E4" t="s">
         <v>116</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="s">
@@ -2498,14 +2508,14 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>129</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="s">
@@ -2514,7 +2524,7 @@
       <c r="E5" t="s">
         <v>148</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="s">
@@ -2524,14 +2534,14 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>129</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="s">
@@ -2540,7 +2550,7 @@
       <c r="E6" t="s">
         <v>148</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="s">
@@ -2550,14 +2560,14 @@
         <v>152</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>129</v>
       </c>
       <c r="B7" t="s">
         <v>49</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="s">
@@ -2566,7 +2576,7 @@
       <c r="E7" t="s">
         <v>153</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="s">
@@ -2576,14 +2586,14 @@
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>130</v>
       </c>
       <c r="B8" t="s">
         <v>105</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="s">
@@ -2592,7 +2602,7 @@
       <c r="E8" t="s">
         <v>116</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="s">
@@ -2602,14 +2612,14 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>130</v>
       </c>
       <c r="B9" t="s">
         <v>105</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="s">
@@ -2618,7 +2628,7 @@
       <c r="E9" t="s">
         <v>116</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="s">
@@ -2628,14 +2638,14 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>130</v>
       </c>
       <c r="B10" t="s">
         <v>105</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="s">
@@ -2644,7 +2654,7 @@
       <c r="E10" t="s">
         <v>116</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="s">
@@ -2654,14 +2664,14 @@
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>130</v>
       </c>
       <c r="B11" t="s">
         <v>105</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="s">
@@ -2670,7 +2680,7 @@
       <c r="E11" t="s">
         <v>148</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="s">
@@ -2680,14 +2690,14 @@
         <v>161</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>130</v>
       </c>
       <c r="B12" t="s">
         <v>105</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="s">
@@ -2696,7 +2706,7 @@
       <c r="E12" t="s">
         <v>148</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>2</v>
       </c>
       <c r="G12" t="s">
@@ -2706,14 +2716,14 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>130</v>
       </c>
       <c r="B13" t="s">
         <v>105</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="s">
@@ -2722,7 +2732,7 @@
       <c r="E13" t="s">
         <v>148</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>3</v>
       </c>
       <c r="G13" t="s">
@@ -2732,14 +2742,14 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>130</v>
       </c>
       <c r="B14" t="s">
         <v>105</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="s">
@@ -2748,7 +2758,7 @@
       <c r="E14" t="s">
         <v>148</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
       <c r="G14" t="s">
@@ -2758,14 +2768,14 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>130</v>
       </c>
       <c r="B15" t="s">
         <v>105</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="s">
@@ -2774,7 +2784,7 @@
       <c r="E15" t="s">
         <v>168</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="s">
@@ -2784,14 +2794,14 @@
         <v>170</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>130</v>
       </c>
       <c r="B16" t="s">
         <v>105</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="s">
@@ -2800,7 +2810,7 @@
       <c r="E16" t="s">
         <v>153</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="s">
@@ -2810,14 +2820,14 @@
         <v>155</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>131</v>
       </c>
       <c r="B17" t="s">
         <v>106</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="s">
@@ -2826,7 +2836,7 @@
       <c r="E17" t="s">
         <v>116</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="s">
@@ -2836,14 +2846,14 @@
         <v>173</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>131</v>
       </c>
       <c r="B18" t="s">
         <v>106</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="s">
@@ -2852,7 +2862,7 @@
       <c r="E18" t="s">
         <v>116</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="s">
@@ -2862,14 +2872,14 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>131</v>
       </c>
       <c r="B19" t="s">
         <v>106</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="s">
@@ -2878,7 +2888,7 @@
       <c r="E19" t="s">
         <v>116</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="s">
@@ -2888,14 +2898,14 @@
         <v>147</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>131</v>
       </c>
       <c r="B20" t="s">
         <v>106</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="s">
@@ -2904,7 +2914,7 @@
       <c r="E20" t="s">
         <v>148</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="s">
@@ -2914,14 +2924,14 @@
         <v>177</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>131</v>
       </c>
       <c r="B21" t="s">
         <v>106</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="s">
@@ -2930,7 +2940,7 @@
       <c r="E21" t="s">
         <v>148</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
       <c r="G21" t="s">
@@ -2940,14 +2950,14 @@
         <v>179</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>131</v>
       </c>
       <c r="B22" t="s">
         <v>106</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="s">
@@ -2956,7 +2966,7 @@
       <c r="E22" t="s">
         <v>148</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="s">
@@ -2966,14 +2976,14 @@
         <v>181</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>131</v>
       </c>
       <c r="B23" t="s">
         <v>106</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="s">
@@ -2982,7 +2992,7 @@
       <c r="E23" t="s">
         <v>168</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="s">
@@ -2992,14 +3002,14 @@
         <v>183</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>131</v>
       </c>
       <c r="B24" t="s">
         <v>106</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="s">
@@ -3008,7 +3018,7 @@
       <c r="E24" t="s">
         <v>153</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="s">
@@ -3018,14 +3028,14 @@
         <v>185</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>132</v>
       </c>
       <c r="B25" t="s">
         <v>107</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="s">
@@ -3034,7 +3044,7 @@
       <c r="E25" t="s">
         <v>116</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="s">
@@ -3044,14 +3054,14 @@
         <v>187</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" t="s">
         <v>132</v>
       </c>
       <c r="B26" t="s">
         <v>107</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="s">
@@ -3060,7 +3070,7 @@
       <c r="E26" t="s">
         <v>116</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>2</v>
       </c>
       <c r="G26" t="s">
@@ -3070,14 +3080,14 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" t="s">
         <v>132</v>
       </c>
       <c r="B27" t="s">
         <v>107</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="s">
@@ -3086,7 +3096,7 @@
       <c r="E27" t="s">
         <v>116</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>3</v>
       </c>
       <c r="G27" t="s">
@@ -3096,14 +3106,14 @@
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" t="s">
         <v>132</v>
       </c>
       <c r="B28" t="s">
         <v>107</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="s">
@@ -3112,7 +3122,7 @@
       <c r="E28" t="s">
         <v>148</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="s">
@@ -3122,14 +3132,14 @@
         <v>191</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" t="s">
         <v>132</v>
       </c>
       <c r="B29" t="s">
         <v>107</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="s">
@@ -3138,7 +3148,7 @@
       <c r="E29" t="s">
         <v>148</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>2</v>
       </c>
       <c r="G29" t="s">
@@ -3148,14 +3158,14 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" t="s">
         <v>132</v>
       </c>
       <c r="B30" t="s">
         <v>107</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="s">
@@ -3164,7 +3174,7 @@
       <c r="E30" t="s">
         <v>148</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>3</v>
       </c>
       <c r="G30" t="s">
@@ -3174,14 +3184,14 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" t="s">
         <v>132</v>
       </c>
       <c r="B31" t="s">
         <v>107</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="s">
@@ -3190,7 +3200,7 @@
       <c r="E31" t="s">
         <v>168</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="s">
@@ -3200,14 +3210,14 @@
         <v>183</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" t="s">
         <v>132</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="s">
@@ -3216,7 +3226,7 @@
       <c r="E32" t="s">
         <v>153</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="s">
@@ -3226,14 +3236,14 @@
         <v>185</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33" t="s">
         <v>133</v>
       </c>
       <c r="B33" t="s">
         <v>108</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="s">
@@ -3242,7 +3252,7 @@
       <c r="E33" t="s">
         <v>116</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="s">
@@ -3252,14 +3262,14 @@
         <v>197</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34" t="s">
         <v>133</v>
       </c>
       <c r="B34" t="s">
         <v>108</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="s">
@@ -3268,7 +3278,7 @@
       <c r="E34" t="s">
         <v>116</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>2</v>
       </c>
       <c r="G34" t="s">
@@ -3278,14 +3288,14 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35">
       <c r="A35" t="s">
         <v>133</v>
       </c>
       <c r="B35" t="s">
         <v>108</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="s">
@@ -3294,7 +3304,7 @@
       <c r="E35" t="s">
         <v>116</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>3</v>
       </c>
       <c r="G35" t="s">
@@ -3304,14 +3314,14 @@
         <v>147</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36">
       <c r="A36" t="s">
         <v>133</v>
       </c>
       <c r="B36" t="s">
         <v>108</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="s">
@@ -3320,7 +3330,7 @@
       <c r="E36" t="s">
         <v>148</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="s">
@@ -3330,14 +3340,14 @@
         <v>201</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37">
       <c r="A37" t="s">
         <v>133</v>
       </c>
       <c r="B37" t="s">
         <v>108</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="s">
@@ -3346,7 +3356,7 @@
       <c r="E37" t="s">
         <v>148</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>2</v>
       </c>
       <c r="G37" t="s">
@@ -3356,14 +3366,14 @@
         <v>179</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38">
       <c r="A38" t="s">
         <v>133</v>
       </c>
       <c r="B38" t="s">
         <v>108</v>
       </c>
-      <c r="C38">
+      <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="s">
@@ -3372,7 +3382,7 @@
       <c r="E38" t="s">
         <v>148</v>
       </c>
-      <c r="F38">
+      <c r="F38" t="n">
         <v>3</v>
       </c>
       <c r="G38" t="s">
@@ -3382,14 +3392,14 @@
         <v>181</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39">
       <c r="A39" t="s">
         <v>133</v>
       </c>
       <c r="B39" t="s">
         <v>108</v>
       </c>
-      <c r="C39">
+      <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="s">
@@ -3398,7 +3408,7 @@
       <c r="E39" t="s">
         <v>168</v>
       </c>
-      <c r="F39">
+      <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" t="s">
@@ -3408,14 +3418,14 @@
         <v>183</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40">
       <c r="A40" t="s">
         <v>133</v>
       </c>
       <c r="B40" t="s">
         <v>108</v>
       </c>
-      <c r="C40">
+      <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="s">
@@ -3424,7 +3434,7 @@
       <c r="E40" t="s">
         <v>153</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="s">
@@ -3436,15 +3446,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
@@ -3463,15 +3474,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
@@ -3493,28 +3505,29 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:K53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" customWidth="1"/>
-    <col min="7" max="7" width="34.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="8" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="34.5546875" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="19.44140625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -3549,7 +3562,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>223</v>
       </c>
@@ -3559,10 +3572,10 @@
       <c r="D2" t="s">
         <v>224</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="s">
@@ -3575,7 +3588,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>228</v>
       </c>
@@ -3585,10 +3598,10 @@
       <c r="D3" t="s">
         <v>229</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="s">
@@ -3601,7 +3614,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>231</v>
       </c>
@@ -3611,10 +3624,10 @@
       <c r="D4" t="s">
         <v>232</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="s">
@@ -3630,7 +3643,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>236</v>
       </c>
@@ -3640,10 +3653,10 @@
       <c r="D5" t="s">
         <v>237</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="s">
@@ -3659,7 +3672,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>238</v>
       </c>
@@ -3669,17 +3682,17 @@
       <c r="D6" t="s">
         <v>239</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>238</v>
       </c>
@@ -3689,10 +3702,10 @@
       <c r="D7" t="s">
         <v>239</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="s">
@@ -3708,7 +3721,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>238</v>
       </c>
@@ -3718,10 +3731,10 @@
       <c r="D8" t="s">
         <v>239</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="s">
@@ -3737,7 +3750,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>243</v>
       </c>
@@ -3747,17 +3760,17 @@
       <c r="D9" t="s">
         <v>237</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>243</v>
       </c>
@@ -3767,10 +3780,10 @@
       <c r="D10" t="s">
         <v>237</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="s">
@@ -3786,7 +3799,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>243</v>
       </c>
@@ -3796,10 +3809,10 @@
       <c r="D11" t="s">
         <v>237</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="s">
@@ -3815,7 +3828,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>243</v>
       </c>
@@ -3825,10 +3838,10 @@
       <c r="D12" t="s">
         <v>237</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>2</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>3</v>
       </c>
       <c r="H12" t="s">
@@ -3841,7 +3854,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>245</v>
       </c>
@@ -3851,17 +3864,17 @@
       <c r="D13" t="s">
         <v>246</v>
       </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>245</v>
       </c>
@@ -3871,10 +3884,10 @@
       <c r="D14" t="s">
         <v>246</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="s">
@@ -3890,7 +3903,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>245</v>
       </c>
@@ -3900,10 +3913,10 @@
       <c r="D15" t="s">
         <v>246</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>2</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="s">
@@ -3919,7 +3932,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>247</v>
       </c>
@@ -3929,17 +3942,17 @@
       <c r="D16" t="s">
         <v>237</v>
       </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>247</v>
       </c>
@@ -3949,10 +3962,10 @@
       <c r="D17" t="s">
         <v>237</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>2</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="s">
@@ -3968,7 +3981,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>247</v>
       </c>
@@ -3978,10 +3991,10 @@
       <c r="D18" t="s">
         <v>237</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>2</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="s">
@@ -3997,7 +4010,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>247</v>
       </c>
@@ -4007,10 +4020,10 @@
       <c r="D19" t="s">
         <v>237</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>2</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="H19" t="s">
@@ -4023,7 +4036,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>248</v>
       </c>
@@ -4033,17 +4046,17 @@
       <c r="D20" t="s">
         <v>249</v>
       </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20">
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>248</v>
       </c>
@@ -4053,10 +4066,10 @@
       <c r="D21" t="s">
         <v>249</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>2</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="s">
@@ -4072,7 +4085,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>248</v>
       </c>
@@ -4082,10 +4095,10 @@
       <c r="D22" t="s">
         <v>249</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>2</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>2</v>
       </c>
       <c r="H22" t="s">
@@ -4098,7 +4111,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>254</v>
       </c>
@@ -4108,17 +4121,17 @@
       <c r="D23" t="s">
         <v>255</v>
       </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>254</v>
       </c>
@@ -4128,10 +4141,10 @@
       <c r="D24" t="s">
         <v>255</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>2</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="s">
@@ -4147,7 +4160,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>254</v>
       </c>
@@ -4157,10 +4170,10 @@
       <c r="D25" t="s">
         <v>255</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>2</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>2</v>
       </c>
       <c r="H25" t="s">
@@ -4176,7 +4189,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" t="s">
         <v>257</v>
       </c>
@@ -4186,10 +4199,10 @@
       <c r="D26" t="s">
         <v>258</v>
       </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26">
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="s">
@@ -4205,7 +4218,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" t="s">
         <v>259</v>
       </c>
@@ -4215,17 +4228,17 @@
       <c r="D27" t="s">
         <v>260</v>
       </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27">
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" t="s">
         <v>259</v>
       </c>
@@ -4235,10 +4248,10 @@
       <c r="D28" t="s">
         <v>260</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>2</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="s">
@@ -4254,7 +4267,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" t="s">
         <v>259</v>
       </c>
@@ -4264,10 +4277,10 @@
       <c r="D29" t="s">
         <v>260</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>2</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="s">
@@ -4283,7 +4296,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" t="s">
         <v>261</v>
       </c>
@@ -4293,10 +4306,10 @@
       <c r="D30" t="s">
         <v>262</v>
       </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30">
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="s">
@@ -4312,7 +4325,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" t="s">
         <v>263</v>
       </c>
@@ -4322,17 +4335,17 @@
       <c r="D31" t="s">
         <v>264</v>
       </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" t="s">
         <v>263</v>
       </c>
@@ -4342,10 +4355,10 @@
       <c r="D32" t="s">
         <v>264</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>2</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="s">
@@ -4361,7 +4374,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33" t="s">
         <v>263</v>
       </c>
@@ -4371,10 +4384,10 @@
       <c r="D33" t="s">
         <v>264</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>2</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>2</v>
       </c>
       <c r="H33" t="s">
@@ -4390,7 +4403,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34" t="s">
         <v>265</v>
       </c>
@@ -4400,10 +4413,10 @@
       <c r="D34" t="s">
         <v>266</v>
       </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34">
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="s">
@@ -4419,7 +4432,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35">
       <c r="A35" t="s">
         <v>267</v>
       </c>
@@ -4429,17 +4442,17 @@
       <c r="D35" t="s">
         <v>268</v>
       </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35">
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36">
       <c r="A36" t="s">
         <v>267</v>
       </c>
@@ -4449,10 +4462,10 @@
       <c r="D36" t="s">
         <v>268</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>2</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="s">
@@ -4468,7 +4481,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37">
       <c r="A37" t="s">
         <v>267</v>
       </c>
@@ -4478,10 +4491,10 @@
       <c r="D37" t="s">
         <v>268</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>2</v>
       </c>
       <c r="H37" t="s">
@@ -4494,7 +4507,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38">
       <c r="A38" t="s">
         <v>270</v>
       </c>
@@ -4504,17 +4517,17 @@
       <c r="D38" t="s">
         <v>255</v>
       </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38">
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39">
       <c r="A39" t="s">
         <v>270</v>
       </c>
@@ -4524,10 +4537,10 @@
       <c r="D39" t="s">
         <v>255</v>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>2</v>
       </c>
-      <c r="F39">
+      <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="s">
@@ -4543,7 +4556,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40">
       <c r="A40" t="s">
         <v>270</v>
       </c>
@@ -4553,10 +4566,10 @@
       <c r="D40" t="s">
         <v>255</v>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>2</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="n">
         <v>2</v>
       </c>
       <c r="H40" t="s">
@@ -4572,7 +4585,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41">
       <c r="A41" t="s">
         <v>271</v>
       </c>
@@ -4582,10 +4595,10 @@
       <c r="D41" t="s">
         <v>258</v>
       </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41">
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="s">
@@ -4601,7 +4614,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42">
       <c r="A42" t="s">
         <v>272</v>
       </c>
@@ -4611,17 +4624,17 @@
       <c r="D42" t="s">
         <v>260</v>
       </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="F42">
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43">
       <c r="A43" t="s">
         <v>272</v>
       </c>
@@ -4631,10 +4644,10 @@
       <c r="D43" t="s">
         <v>260</v>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>2</v>
       </c>
-      <c r="F43">
+      <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="H43" t="s">
@@ -4650,7 +4663,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44">
       <c r="A44" t="s">
         <v>272</v>
       </c>
@@ -4660,10 +4673,10 @@
       <c r="D44" t="s">
         <v>260</v>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>2</v>
       </c>
-      <c r="F44">
+      <c r="F44" t="n">
         <v>2</v>
       </c>
       <c r="H44" t="s">
@@ -4679,7 +4692,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45">
       <c r="A45" t="s">
         <v>273</v>
       </c>
@@ -4689,10 +4702,10 @@
       <c r="D45" t="s">
         <v>262</v>
       </c>
-      <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="F45">
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="s">
@@ -4708,7 +4721,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46">
       <c r="A46" t="s">
         <v>274</v>
       </c>
@@ -4718,17 +4731,17 @@
       <c r="D46" t="s">
         <v>264</v>
       </c>
-      <c r="E46">
-        <v>1</v>
-      </c>
-      <c r="F46">
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47">
       <c r="A47" t="s">
         <v>274</v>
       </c>
@@ -4738,10 +4751,10 @@
       <c r="D47" t="s">
         <v>264</v>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>2</v>
       </c>
-      <c r="F47">
+      <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="s">
@@ -4757,7 +4770,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48">
       <c r="A48" t="s">
         <v>274</v>
       </c>
@@ -4767,10 +4780,10 @@
       <c r="D48" t="s">
         <v>264</v>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>2</v>
       </c>
-      <c r="F48">
+      <c r="F48" t="n">
         <v>2</v>
       </c>
       <c r="H48" t="s">
@@ -4786,7 +4799,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49">
       <c r="A49" t="s">
         <v>275</v>
       </c>
@@ -4796,10 +4809,10 @@
       <c r="D49" t="s">
         <v>266</v>
       </c>
-      <c r="E49">
-        <v>1</v>
-      </c>
-      <c r="F49">
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="s">
@@ -4815,7 +4828,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50">
       <c r="A50" t="s">
         <v>276</v>
       </c>
@@ -4825,10 +4838,10 @@
       <c r="D50" t="s">
         <v>249</v>
       </c>
-      <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="F50">
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="s">
@@ -4841,7 +4854,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51">
       <c r="A51" t="s">
         <v>278</v>
       </c>
@@ -4851,10 +4864,10 @@
       <c r="D51" t="s">
         <v>255</v>
       </c>
-      <c r="E51">
-        <v>1</v>
-      </c>
-      <c r="F51">
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="s">
@@ -4870,7 +4883,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52">
       <c r="A52" t="s">
         <v>279</v>
       </c>
@@ -4880,10 +4893,10 @@
       <c r="D52" t="s">
         <v>260</v>
       </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="F52">
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="s">
@@ -4899,7 +4912,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53">
       <c r="A53" t="s">
         <v>280</v>
       </c>
@@ -4909,10 +4922,10 @@
       <c r="D53" t="s">
         <v>264</v>
       </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="F53">
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="H53" t="s">
@@ -4930,32 +4943,34 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:P80"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.88671875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="29.5546875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="27.77734375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="36.88671875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="36.88671875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.21875" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="40.6640625" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="22.88671875" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="23.44140625" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="26.5546875" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="36.88671875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -5005,7 +5020,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>304</v>
       </c>
@@ -5027,10 +5042,10 @@
       <c r="H2" t="s">
         <v>308</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="s">
@@ -5046,7 +5061,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>304</v>
       </c>
@@ -5068,10 +5083,10 @@
       <c r="H3" t="s">
         <v>311</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="M3" t="s">
@@ -5087,7 +5102,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>304</v>
       </c>
@@ -5109,10 +5124,10 @@
       <c r="H4" t="s">
         <v>314</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
       </c>
       <c r="M4" t="s">
@@ -5128,7 +5143,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>316</v>
       </c>
@@ -5156,10 +5171,10 @@
       <c r="I5" t="s">
         <v>321</v>
       </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="s">
@@ -5175,7 +5190,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>316</v>
       </c>
@@ -5203,10 +5218,10 @@
       <c r="I6" t="s">
         <v>323</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
       <c r="M6" t="s">
@@ -5222,7 +5237,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>316</v>
       </c>
@@ -5250,10 +5265,10 @@
       <c r="I7" t="s">
         <v>325</v>
       </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
       <c r="M7" t="s">
@@ -5269,7 +5284,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>316</v>
       </c>
@@ -5297,10 +5312,10 @@
       <c r="I8" t="s">
         <v>327</v>
       </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
         <v>4</v>
       </c>
       <c r="M8" t="s">
@@ -5316,7 +5331,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>328</v>
       </c>
@@ -5344,10 +5359,10 @@
       <c r="I9" t="s">
         <v>333</v>
       </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="s">
@@ -5363,7 +5378,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>328</v>
       </c>
@@ -5391,10 +5406,10 @@
       <c r="I10" t="s">
         <v>336</v>
       </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
         <v>2</v>
       </c>
       <c r="M10" t="s">
@@ -5410,7 +5425,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>328</v>
       </c>
@@ -5438,10 +5453,10 @@
       <c r="I11" t="s">
         <v>338</v>
       </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11">
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>3</v>
       </c>
       <c r="M11" t="s">
@@ -5457,7 +5472,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>339</v>
       </c>
@@ -5485,10 +5500,10 @@
       <c r="I12" t="s">
         <v>344</v>
       </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12">
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="s">
@@ -5504,7 +5519,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>339</v>
       </c>
@@ -5532,10 +5547,10 @@
       <c r="I13" t="s">
         <v>346</v>
       </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
       </c>
       <c r="M13" t="s">
@@ -5551,7 +5566,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>339</v>
       </c>
@@ -5579,10 +5594,10 @@
       <c r="I14" t="s">
         <v>348</v>
       </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>3</v>
       </c>
       <c r="M14" t="s">
@@ -5598,7 +5613,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>339</v>
       </c>
@@ -5626,10 +5641,10 @@
       <c r="I15" t="s">
         <v>350</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
         <v>4</v>
       </c>
       <c r="M15" t="s">
@@ -5645,7 +5660,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>339</v>
       </c>
@@ -5673,10 +5688,10 @@
       <c r="I16" t="s">
         <v>352</v>
       </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
         <v>5</v>
       </c>
       <c r="M16" t="s">
@@ -5692,7 +5707,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>339</v>
       </c>
@@ -5720,10 +5735,10 @@
       <c r="I17" t="s">
         <v>354</v>
       </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17">
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
         <v>6</v>
       </c>
       <c r="M17" t="s">
@@ -5739,7 +5754,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>339</v>
       </c>
@@ -5767,10 +5782,10 @@
       <c r="I18" t="s">
         <v>356</v>
       </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>7</v>
       </c>
       <c r="M18" t="s">
@@ -5786,7 +5801,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>339</v>
       </c>
@@ -5814,10 +5829,10 @@
       <c r="I19" t="s">
         <v>327</v>
       </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
         <v>8</v>
       </c>
       <c r="M19" t="s">
@@ -5833,7 +5848,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>358</v>
       </c>
@@ -5861,10 +5876,10 @@
       <c r="I20" t="s">
         <v>363</v>
       </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="s">
@@ -5880,7 +5895,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>358</v>
       </c>
@@ -5908,10 +5923,10 @@
       <c r="I21" t="s">
         <v>365</v>
       </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
       <c r="M21" t="s">
@@ -5927,7 +5942,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>358</v>
       </c>
@@ -5955,10 +5970,10 @@
       <c r="I22" t="s">
         <v>356</v>
       </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
         <v>3</v>
       </c>
       <c r="M22" t="s">
@@ -5974,7 +5989,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>358</v>
       </c>
@@ -6002,10 +6017,10 @@
       <c r="I23" t="s">
         <v>327</v>
       </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
         <v>4</v>
       </c>
       <c r="M23" t="s">
@@ -6021,7 +6036,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>368</v>
       </c>
@@ -6049,10 +6064,10 @@
       <c r="I24" t="s">
         <v>373</v>
       </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24">
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="M24" t="s">
@@ -6068,7 +6083,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>374</v>
       </c>
@@ -6090,10 +6105,10 @@
       <c r="H25" t="s">
         <v>308</v>
       </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25">
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="M25" t="s">
@@ -6109,7 +6124,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" t="s">
         <v>374</v>
       </c>
@@ -6131,10 +6146,10 @@
       <c r="H26" t="s">
         <v>311</v>
       </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26">
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
         <v>2</v>
       </c>
       <c r="M26" t="s">
@@ -6150,7 +6165,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" t="s">
         <v>374</v>
       </c>
@@ -6172,10 +6187,10 @@
       <c r="H27" t="s">
         <v>314</v>
       </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
         <v>3</v>
       </c>
       <c r="M27" t="s">
@@ -6191,7 +6206,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" t="s">
         <v>378</v>
       </c>
@@ -6219,10 +6234,10 @@
       <c r="I28" t="s">
         <v>232</v>
       </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-      <c r="K28">
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="M28" t="s">
@@ -6238,7 +6253,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" t="s">
         <v>381</v>
       </c>
@@ -6266,10 +6281,10 @@
       <c r="I29" t="s">
         <v>237</v>
       </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29">
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="M29" t="s">
@@ -6285,7 +6300,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" t="s">
         <v>385</v>
       </c>
@@ -6313,17 +6328,17 @@
       <c r="I30" t="s">
         <v>239</v>
       </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" t="s">
         <v>385</v>
       </c>
@@ -6351,10 +6366,10 @@
       <c r="I31" t="s">
         <v>239</v>
       </c>
-      <c r="J31">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="M31" t="s">
@@ -6370,7 +6385,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" t="s">
         <v>385</v>
       </c>
@@ -6398,10 +6413,10 @@
       <c r="I32" t="s">
         <v>239</v>
       </c>
-      <c r="J32">
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="n">
         <v>2</v>
       </c>
       <c r="M32" t="s">
@@ -6417,7 +6432,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33" t="s">
         <v>388</v>
       </c>
@@ -6445,17 +6460,17 @@
       <c r="I33" t="s">
         <v>237</v>
       </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
-      <c r="K33">
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34" t="s">
         <v>388</v>
       </c>
@@ -6483,10 +6498,10 @@
       <c r="I34" t="s">
         <v>237</v>
       </c>
-      <c r="J34">
+      <c r="J34" t="n">
         <v>2</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="s">
@@ -6502,7 +6517,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35">
       <c r="A35" t="s">
         <v>388</v>
       </c>
@@ -6530,10 +6545,10 @@
       <c r="I35" t="s">
         <v>237</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="n">
         <v>2</v>
       </c>
       <c r="M35" t="s">
@@ -6549,7 +6564,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36">
       <c r="A36" t="s">
         <v>388</v>
       </c>
@@ -6577,10 +6592,10 @@
       <c r="I36" t="s">
         <v>237</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="n">
         <v>3</v>
       </c>
       <c r="M36" t="s">
@@ -6593,7 +6608,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37">
       <c r="A37" t="s">
         <v>390</v>
       </c>
@@ -6621,17 +6636,17 @@
       <c r="I37" t="s">
         <v>246</v>
       </c>
-      <c r="J37">
-        <v>1</v>
-      </c>
-      <c r="K37">
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38">
       <c r="A38" t="s">
         <v>390</v>
       </c>
@@ -6659,10 +6674,10 @@
       <c r="I38" t="s">
         <v>246</v>
       </c>
-      <c r="J38">
+      <c r="J38" t="n">
         <v>2</v>
       </c>
-      <c r="K38">
+      <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="s">
@@ -6678,7 +6693,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39">
       <c r="A39" t="s">
         <v>390</v>
       </c>
@@ -6706,10 +6721,10 @@
       <c r="I39" t="s">
         <v>246</v>
       </c>
-      <c r="J39">
+      <c r="J39" t="n">
         <v>2</v>
       </c>
-      <c r="K39">
+      <c r="K39" t="n">
         <v>2</v>
       </c>
       <c r="M39" t="s">
@@ -6725,7 +6740,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40">
       <c r="A40" t="s">
         <v>392</v>
       </c>
@@ -6753,17 +6768,17 @@
       <c r="I40" t="s">
         <v>237</v>
       </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="K40">
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41">
       <c r="A41" t="s">
         <v>392</v>
       </c>
@@ -6791,10 +6806,10 @@
       <c r="I41" t="s">
         <v>237</v>
       </c>
-      <c r="J41">
+      <c r="J41" t="n">
         <v>2</v>
       </c>
-      <c r="K41">
+      <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="s">
@@ -6810,7 +6825,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42">
       <c r="A42" t="s">
         <v>392</v>
       </c>
@@ -6838,10 +6853,10 @@
       <c r="I42" t="s">
         <v>237</v>
       </c>
-      <c r="J42">
+      <c r="J42" t="n">
         <v>2</v>
       </c>
-      <c r="K42">
+      <c r="K42" t="n">
         <v>2</v>
       </c>
       <c r="M42" t="s">
@@ -6857,7 +6872,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43">
       <c r="A43" t="s">
         <v>392</v>
       </c>
@@ -6885,10 +6900,10 @@
       <c r="I43" t="s">
         <v>237</v>
       </c>
-      <c r="J43">
+      <c r="J43" t="n">
         <v>2</v>
       </c>
-      <c r="K43">
+      <c r="K43" t="n">
         <v>3</v>
       </c>
       <c r="M43" t="s">
@@ -6901,7 +6916,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44">
       <c r="A44" t="s">
         <v>394</v>
       </c>
@@ -6923,10 +6938,10 @@
       <c r="H44" t="s">
         <v>396</v>
       </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-      <c r="K44">
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="s">
@@ -6942,7 +6957,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45">
       <c r="A45" t="s">
         <v>394</v>
       </c>
@@ -6964,10 +6979,10 @@
       <c r="H45" t="s">
         <v>398</v>
       </c>
-      <c r="J45">
-        <v>1</v>
-      </c>
-      <c r="K45">
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
         <v>2</v>
       </c>
       <c r="M45" t="s">
@@ -6983,7 +6998,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46">
       <c r="A46" t="s">
         <v>394</v>
       </c>
@@ -7005,10 +7020,10 @@
       <c r="H46" t="s">
         <v>400</v>
       </c>
-      <c r="J46">
-        <v>1</v>
-      </c>
-      <c r="K46">
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
         <v>3</v>
       </c>
       <c r="M46" t="s">
@@ -7024,7 +7039,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47">
       <c r="A47" t="s">
         <v>401</v>
       </c>
@@ -7052,17 +7067,17 @@
       <c r="I47" t="s">
         <v>249</v>
       </c>
-      <c r="J47">
-        <v>1</v>
-      </c>
-      <c r="K47">
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48">
       <c r="A48" t="s">
         <v>401</v>
       </c>
@@ -7090,10 +7105,10 @@
       <c r="I48" t="s">
         <v>249</v>
       </c>
-      <c r="J48">
+      <c r="J48" t="n">
         <v>2</v>
       </c>
-      <c r="K48">
+      <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="M48" t="s">
@@ -7109,7 +7124,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49">
       <c r="A49" t="s">
         <v>401</v>
       </c>
@@ -7137,10 +7152,10 @@
       <c r="I49" t="s">
         <v>249</v>
       </c>
-      <c r="J49">
+      <c r="J49" t="n">
         <v>2</v>
       </c>
-      <c r="K49">
+      <c r="K49" t="n">
         <v>2</v>
       </c>
       <c r="M49" t="s">
@@ -7153,7 +7168,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50">
       <c r="A50" t="s">
         <v>404</v>
       </c>
@@ -7181,17 +7196,17 @@
       <c r="I50" t="s">
         <v>255</v>
       </c>
-      <c r="J50">
-        <v>1</v>
-      </c>
-      <c r="K50">
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51">
       <c r="A51" t="s">
         <v>404</v>
       </c>
@@ -7219,10 +7234,10 @@
       <c r="I51" t="s">
         <v>255</v>
       </c>
-      <c r="J51">
+      <c r="J51" t="n">
         <v>2</v>
       </c>
-      <c r="K51">
+      <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="M51" t="s">
@@ -7238,7 +7253,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52">
       <c r="A52" t="s">
         <v>404</v>
       </c>
@@ -7266,10 +7281,10 @@
       <c r="I52" t="s">
         <v>255</v>
       </c>
-      <c r="J52">
+      <c r="J52" t="n">
         <v>2</v>
       </c>
-      <c r="K52">
+      <c r="K52" t="n">
         <v>2</v>
       </c>
       <c r="M52" t="s">
@@ -7285,7 +7300,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53">
       <c r="A53" t="s">
         <v>407</v>
       </c>
@@ -7313,17 +7328,17 @@
       <c r="I53" t="s">
         <v>260</v>
       </c>
-      <c r="J53">
-        <v>1</v>
-      </c>
-      <c r="K53">
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54">
       <c r="A54" t="s">
         <v>407</v>
       </c>
@@ -7351,10 +7366,10 @@
       <c r="I54" t="s">
         <v>260</v>
       </c>
-      <c r="J54">
+      <c r="J54" t="n">
         <v>2</v>
       </c>
-      <c r="K54">
+      <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="M54" t="s">
@@ -7370,7 +7385,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55">
       <c r="A55" t="s">
         <v>407</v>
       </c>
@@ -7398,10 +7413,10 @@
       <c r="I55" t="s">
         <v>260</v>
       </c>
-      <c r="J55">
+      <c r="J55" t="n">
         <v>2</v>
       </c>
-      <c r="K55">
+      <c r="K55" t="n">
         <v>2</v>
       </c>
       <c r="M55" t="s">
@@ -7417,7 +7432,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56">
       <c r="A56" t="s">
         <v>409</v>
       </c>
@@ -7445,17 +7460,17 @@
       <c r="I56" t="s">
         <v>264</v>
       </c>
-      <c r="J56">
-        <v>1</v>
-      </c>
-      <c r="K56">
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57">
       <c r="A57" t="s">
         <v>409</v>
       </c>
@@ -7483,10 +7498,10 @@
       <c r="I57" t="s">
         <v>264</v>
       </c>
-      <c r="J57">
+      <c r="J57" t="n">
         <v>2</v>
       </c>
-      <c r="K57">
+      <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="M57" t="s">
@@ -7502,7 +7517,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58">
       <c r="A58" t="s">
         <v>409</v>
       </c>
@@ -7530,10 +7545,10 @@
       <c r="I58" t="s">
         <v>264</v>
       </c>
-      <c r="J58">
+      <c r="J58" t="n">
         <v>2</v>
       </c>
-      <c r="K58">
+      <c r="K58" t="n">
         <v>2</v>
       </c>
       <c r="M58" t="s">
@@ -7549,7 +7564,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59">
       <c r="A59" t="s">
         <v>411</v>
       </c>
@@ -7571,10 +7586,10 @@
       <c r="H59" t="s">
         <v>396</v>
       </c>
-      <c r="J59">
-        <v>1</v>
-      </c>
-      <c r="K59">
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="s">
@@ -7590,7 +7605,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60">
       <c r="A60" t="s">
         <v>411</v>
       </c>
@@ -7612,10 +7627,10 @@
       <c r="H60" t="s">
         <v>398</v>
       </c>
-      <c r="J60">
-        <v>1</v>
-      </c>
-      <c r="K60">
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
         <v>2</v>
       </c>
       <c r="M60" t="s">
@@ -7631,7 +7646,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61">
       <c r="A61" t="s">
         <v>411</v>
       </c>
@@ -7653,10 +7668,10 @@
       <c r="H61" t="s">
         <v>400</v>
       </c>
-      <c r="J61">
-        <v>1</v>
-      </c>
-      <c r="K61">
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
         <v>3</v>
       </c>
       <c r="M61" t="s">
@@ -7672,7 +7687,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62">
       <c r="A62" t="s">
         <v>415</v>
       </c>
@@ -7700,17 +7715,17 @@
       <c r="I62" t="s">
         <v>268</v>
       </c>
-      <c r="J62">
-        <v>1</v>
-      </c>
-      <c r="K62">
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63">
       <c r="A63" t="s">
         <v>415</v>
       </c>
@@ -7738,10 +7753,10 @@
       <c r="I63" t="s">
         <v>268</v>
       </c>
-      <c r="J63">
+      <c r="J63" t="n">
         <v>2</v>
       </c>
-      <c r="K63">
+      <c r="K63" t="n">
         <v>1</v>
       </c>
       <c r="M63" t="s">
@@ -7757,7 +7772,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64">
       <c r="A64" t="s">
         <v>415</v>
       </c>
@@ -7785,10 +7800,10 @@
       <c r="I64" t="s">
         <v>268</v>
       </c>
-      <c r="J64">
+      <c r="J64" t="n">
         <v>2</v>
       </c>
-      <c r="K64">
+      <c r="K64" t="n">
         <v>2</v>
       </c>
       <c r="M64" t="s">
@@ -7801,7 +7816,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65">
       <c r="A65" t="s">
         <v>417</v>
       </c>
@@ -7829,17 +7844,17 @@
       <c r="I65" t="s">
         <v>255</v>
       </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-      <c r="K65">
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66">
       <c r="A66" t="s">
         <v>417</v>
       </c>
@@ -7867,10 +7882,10 @@
       <c r="I66" t="s">
         <v>255</v>
       </c>
-      <c r="J66">
+      <c r="J66" t="n">
         <v>2</v>
       </c>
-      <c r="K66">
+      <c r="K66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="s">
@@ -7886,7 +7901,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67">
       <c r="A67" t="s">
         <v>417</v>
       </c>
@@ -7914,10 +7929,10 @@
       <c r="I67" t="s">
         <v>255</v>
       </c>
-      <c r="J67">
+      <c r="J67" t="n">
         <v>2</v>
       </c>
-      <c r="K67">
+      <c r="K67" t="n">
         <v>2</v>
       </c>
       <c r="M67" t="s">
@@ -7933,7 +7948,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68">
       <c r="A68" t="s">
         <v>419</v>
       </c>
@@ -7961,17 +7976,17 @@
       <c r="I68" t="s">
         <v>260</v>
       </c>
-      <c r="J68">
-        <v>1</v>
-      </c>
-      <c r="K68">
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69">
       <c r="A69" t="s">
         <v>419</v>
       </c>
@@ -7999,10 +8014,10 @@
       <c r="I69" t="s">
         <v>260</v>
       </c>
-      <c r="J69">
+      <c r="J69" t="n">
         <v>2</v>
       </c>
-      <c r="K69">
+      <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="s">
@@ -8018,7 +8033,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70">
       <c r="A70" t="s">
         <v>419</v>
       </c>
@@ -8046,10 +8061,10 @@
       <c r="I70" t="s">
         <v>260</v>
       </c>
-      <c r="J70">
+      <c r="J70" t="n">
         <v>2</v>
       </c>
-      <c r="K70">
+      <c r="K70" t="n">
         <v>2</v>
       </c>
       <c r="M70" t="s">
@@ -8065,7 +8080,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71">
       <c r="A71" t="s">
         <v>421</v>
       </c>
@@ -8093,17 +8108,17 @@
       <c r="I71" t="s">
         <v>264</v>
       </c>
-      <c r="J71">
-        <v>1</v>
-      </c>
-      <c r="K71">
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72">
       <c r="A72" t="s">
         <v>421</v>
       </c>
@@ -8131,10 +8146,10 @@
       <c r="I72" t="s">
         <v>264</v>
       </c>
-      <c r="J72">
+      <c r="J72" t="n">
         <v>2</v>
       </c>
-      <c r="K72">
+      <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="s">
@@ -8150,7 +8165,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73">
       <c r="A73" t="s">
         <v>421</v>
       </c>
@@ -8178,10 +8193,10 @@
       <c r="I73" t="s">
         <v>264</v>
       </c>
-      <c r="J73">
+      <c r="J73" t="n">
         <v>2</v>
       </c>
-      <c r="K73">
+      <c r="K73" t="n">
         <v>2</v>
       </c>
       <c r="M73" t="s">
@@ -8197,7 +8212,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74">
       <c r="A74" t="s">
         <v>423</v>
       </c>
@@ -8219,10 +8234,10 @@
       <c r="H74" t="s">
         <v>396</v>
       </c>
-      <c r="J74">
-        <v>1</v>
-      </c>
-      <c r="K74">
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="s">
@@ -8238,7 +8253,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75">
       <c r="A75" t="s">
         <v>423</v>
       </c>
@@ -8260,10 +8275,10 @@
       <c r="H75" t="s">
         <v>398</v>
       </c>
-      <c r="J75">
-        <v>1</v>
-      </c>
-      <c r="K75">
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
         <v>2</v>
       </c>
       <c r="M75" t="s">
@@ -8279,7 +8294,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76">
       <c r="A76" t="s">
         <v>423</v>
       </c>
@@ -8301,10 +8316,10 @@
       <c r="H76" t="s">
         <v>400</v>
       </c>
-      <c r="J76">
-        <v>1</v>
-      </c>
-      <c r="K76">
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="n">
         <v>3</v>
       </c>
       <c r="M76" t="s">
@@ -8320,7 +8335,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77">
       <c r="A77" t="s">
         <v>427</v>
       </c>
@@ -8348,10 +8363,10 @@
       <c r="I77" t="s">
         <v>249</v>
       </c>
-      <c r="J77">
-        <v>1</v>
-      </c>
-      <c r="K77">
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
@@ -8364,7 +8379,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78">
       <c r="A78" t="s">
         <v>429</v>
       </c>
@@ -8392,10 +8407,10 @@
       <c r="I78" t="s">
         <v>255</v>
       </c>
-      <c r="J78">
-        <v>1</v>
-      </c>
-      <c r="K78">
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="s">
@@ -8411,7 +8426,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79">
       <c r="A79" t="s">
         <v>431</v>
       </c>
@@ -8439,10 +8454,10 @@
       <c r="I79" t="s">
         <v>260</v>
       </c>
-      <c r="J79">
-        <v>1</v>
-      </c>
-      <c r="K79">
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="M79" t="s">
@@ -8458,7 +8473,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80">
       <c r="A80" t="s">
         <v>433</v>
       </c>
@@ -8486,10 +8501,10 @@
       <c r="I80" t="s">
         <v>264</v>
       </c>
-      <c r="J80">
-        <v>1</v>
-      </c>
-      <c r="K80">
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="s">
@@ -8507,40 +8522,41 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="94.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="50.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="38.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="50.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="37" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="94.21875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="29.21875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="26.77734375" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="23.33203125" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="22.5546875" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="11.21875" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="7.21875" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="9.77734375" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="10.21875" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="50.5546875" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="38.5546875" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="50.5546875" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="37" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -8611,11 +8627,11 @@
         <v>453</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>52</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -8639,15 +8655,15 @@
       <c r="R2" t="s">
         <v>455</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="3" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -8674,11 +8690,11 @@
         <v>456</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>57</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -8726,15 +8742,15 @@
       <c r="V4" t="s">
         <v>463</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -8783,11 +8799,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>62</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -8817,15 +8833,15 @@
       <c r="R6" t="s">
         <v>466</v>
       </c>
-      <c r="S6" t="s">
+      <c r="S6" s="2" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -8856,11 +8872,11 @@
         <v>467</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>67</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
@@ -8908,15 +8924,15 @@
       <c r="V8" t="s">
         <v>463</v>
       </c>
-      <c r="W8" t="s">
+      <c r="W8" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -8965,11 +8981,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>72</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="s">
@@ -9017,15 +9033,15 @@
       <c r="V10" t="s">
         <v>463</v>
       </c>
-      <c r="W10" t="s">
+      <c r="W10" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -9074,11 +9090,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>77</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="s">
@@ -9130,11 +9146,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>79</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="s">
@@ -9183,11 +9199,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>82</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="s">
@@ -9239,11 +9255,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>84</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="s">
@@ -9279,15 +9295,24 @@
       <c r="S15" t="s">
         <v>461</v>
       </c>
+      <c r="T15" t="s">
+        <v>616</v>
+      </c>
+      <c r="U15" t="s">
+        <v>617</v>
+      </c>
+      <c r="V15" t="s">
+        <v>618</v>
+      </c>
       <c r="W15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>87</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="s">
@@ -9321,11 +9346,11 @@
         <v>467</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>89</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="s">
@@ -9356,11 +9381,11 @@
         <v>467</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>92</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="s">
@@ -9394,11 +9419,11 @@
         <v>467</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>94</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="s">
@@ -9429,11 +9454,11 @@
         <v>467</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>97</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="s">
@@ -9467,11 +9492,11 @@
         <v>467</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>99</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="s">
@@ -9502,11 +9527,11 @@
         <v>467</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>102</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="s">
@@ -9543,11 +9568,11 @@
         <v>467</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>104</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="s">
@@ -9580,27 +9605,28 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="78.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="78.5546875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="5.21875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="34.5546875" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="20.21875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="15" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -9632,7 +9658,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>281</v>
       </c>
@@ -9642,10 +9668,10 @@
       <c r="C2" t="s">
         <v>282</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="s">
@@ -9661,17 +9687,17 @@
         <v>235</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>284</v>
       </c>
       <c r="B3" t="s">
         <v>285</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="s">
@@ -9684,7 +9710,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>287</v>
       </c>
@@ -9694,10 +9720,10 @@
       <c r="C4" t="s">
         <v>289</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="s">
@@ -9715,15 +9741,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>488</v>
       </c>
@@ -9739,15 +9766,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>488</v>
       </c>
@@ -9766,15 +9794,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -9797,7 +9826,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -9819,15 +9848,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>488</v>
       </c>
@@ -9849,34 +9879,35 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:Q34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="88.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="41.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="63" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="50.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="156.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="41.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="63" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="50.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="201.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="38.88671875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="37.33203125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="88.21875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="22.21875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="41.77734375" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="63" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="50.5546875" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="156.5546875" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="41.77734375" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="63" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="50.5546875" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="201.33203125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -9929,7 +9960,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>456</v>
       </c>
@@ -9948,7 +9979,7 @@
       <c r="F2" t="s">
         <v>506</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="s">
@@ -9958,7 +9989,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>461</v>
       </c>
@@ -9977,7 +10008,7 @@
       <c r="F3" t="s">
         <v>507</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="s">
@@ -9987,7 +10018,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>461</v>
       </c>
@@ -10006,7 +10037,7 @@
       <c r="F4" t="s">
         <v>515</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="s">
@@ -10040,7 +10071,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>461</v>
       </c>
@@ -10059,7 +10090,7 @@
       <c r="F5" t="s">
         <v>522</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="s">
@@ -10069,7 +10100,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>461</v>
       </c>
@@ -10088,7 +10119,7 @@
       <c r="F6" t="s">
         <v>525</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>4</v>
       </c>
       <c r="H6" t="s">
@@ -10098,7 +10129,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>461</v>
       </c>
@@ -10117,7 +10148,7 @@
       <c r="F7" t="s">
         <v>527</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="s">
@@ -10127,7 +10158,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>528</v>
       </c>
@@ -10146,7 +10177,7 @@
       <c r="F8" t="s">
         <v>507</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="s">
@@ -10156,7 +10187,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>528</v>
       </c>
@@ -10175,7 +10206,7 @@
       <c r="F9" t="s">
         <v>515</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="s">
@@ -10209,7 +10240,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>534</v>
       </c>
@@ -10228,7 +10259,7 @@
       <c r="F10" t="s">
         <v>507</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="s">
@@ -10238,7 +10269,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>534</v>
       </c>
@@ -10257,7 +10288,7 @@
       <c r="F11" t="s">
         <v>515</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="s">
@@ -10291,7 +10322,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>467</v>
       </c>
@@ -10310,7 +10341,7 @@
       <c r="F12" t="s">
         <v>507</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="s">
@@ -10320,7 +10351,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>467</v>
       </c>
@@ -10339,7 +10370,7 @@
       <c r="F13" t="s">
         <v>544</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="s">
@@ -10349,7 +10380,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>467</v>
       </c>
@@ -10368,7 +10399,7 @@
       <c r="F14" t="s">
         <v>546</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>3</v>
       </c>
       <c r="H14" t="s">
@@ -10378,7 +10409,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>467</v>
       </c>
@@ -10397,7 +10428,7 @@
       <c r="F15" t="s">
         <v>548</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>4</v>
       </c>
       <c r="H15" t="s">
@@ -10407,7 +10438,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>467</v>
       </c>
@@ -10426,7 +10457,7 @@
       <c r="F16" t="s">
         <v>550</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>5</v>
       </c>
       <c r="H16" t="s">
@@ -10436,7 +10467,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>467</v>
       </c>
@@ -10455,7 +10486,7 @@
       <c r="F17" t="s">
         <v>552</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>6</v>
       </c>
       <c r="H17" t="s">
@@ -10465,7 +10496,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>467</v>
       </c>
@@ -10484,7 +10515,7 @@
       <c r="F18" t="s">
         <v>554</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>7</v>
       </c>
       <c r="H18" t="s">
@@ -10494,7 +10525,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>467</v>
       </c>
@@ -10513,7 +10544,7 @@
       <c r="F19" t="s">
         <v>556</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="n">
         <v>8</v>
       </c>
       <c r="H19" t="s">
@@ -10523,7 +10554,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>557</v>
       </c>
@@ -10542,7 +10573,7 @@
       <c r="F20" t="s">
         <v>544</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="s">
@@ -10552,7 +10583,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>557</v>
       </c>
@@ -10571,7 +10602,7 @@
       <c r="F21" t="s">
         <v>546</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="s">
@@ -10581,7 +10612,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>557</v>
       </c>
@@ -10600,7 +10631,7 @@
       <c r="F22" t="s">
         <v>548</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>3</v>
       </c>
       <c r="H22" t="s">
@@ -10610,7 +10641,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>557</v>
       </c>
@@ -10629,7 +10660,7 @@
       <c r="F23" t="s">
         <v>554</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>4</v>
       </c>
       <c r="H23" t="s">
@@ -10639,7 +10670,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>557</v>
       </c>
@@ -10658,7 +10689,7 @@
       <c r="F24" t="s">
         <v>556</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>5</v>
       </c>
       <c r="H24" t="s">
@@ -10668,7 +10699,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>557</v>
       </c>
@@ -10687,7 +10718,7 @@
       <c r="F25" t="s">
         <v>550</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>6</v>
       </c>
       <c r="H25" t="s">
@@ -10697,7 +10728,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" t="s">
         <v>557</v>
       </c>
@@ -10716,7 +10747,7 @@
       <c r="F26" t="s">
         <v>552</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>7</v>
       </c>
       <c r="H26" t="s">
@@ -10726,7 +10757,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" t="s">
         <v>565</v>
       </c>
@@ -10745,7 +10776,7 @@
       <c r="F27" t="s">
         <v>507</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="s">
@@ -10755,7 +10786,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" t="s">
         <v>565</v>
       </c>
@@ -10774,7 +10805,7 @@
       <c r="F28" t="s">
         <v>544</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="s">
@@ -10784,7 +10815,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" t="s">
         <v>565</v>
       </c>
@@ -10803,7 +10834,7 @@
       <c r="F29" t="s">
         <v>546</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
       <c r="H29" t="s">
@@ -10813,7 +10844,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" t="s">
         <v>565</v>
       </c>
@@ -10832,7 +10863,7 @@
       <c r="F30" t="s">
         <v>548</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>4</v>
       </c>
       <c r="H30" t="s">
@@ -10842,7 +10873,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" t="s">
         <v>565</v>
       </c>
@@ -10861,7 +10892,7 @@
       <c r="F31" t="s">
         <v>550</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>5</v>
       </c>
       <c r="H31" t="s">
@@ -10871,7 +10902,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" t="s">
         <v>565</v>
       </c>
@@ -10890,7 +10921,7 @@
       <c r="F32" t="s">
         <v>552</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>6</v>
       </c>
       <c r="H32" t="s">
@@ -10900,7 +10931,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33" t="s">
         <v>565</v>
       </c>
@@ -10919,7 +10950,7 @@
       <c r="F33" t="s">
         <v>554</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>7</v>
       </c>
       <c r="H33" t="s">
@@ -10929,7 +10960,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34" t="s">
         <v>565</v>
       </c>
@@ -10948,7 +10979,7 @@
       <c r="F34" t="s">
         <v>556</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>8</v>
       </c>
       <c r="H34" t="s">
@@ -10960,21 +10991,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="8" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="11" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="255.77734375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>449</v>
       </c>
@@ -10988,7 +11020,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>456</v>
       </c>
@@ -11002,7 +11034,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>461</v>
       </c>
@@ -11016,7 +11048,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>467</v>
       </c>
@@ -11032,23 +11064,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="65.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="65.5546875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>449</v>
       </c>
@@ -11068,7 +11101,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>456</v>
       </c>
@@ -11079,7 +11112,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>456</v>
       </c>
@@ -11090,7 +11123,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>461</v>
       </c>
@@ -11104,7 +11137,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>461</v>
       </c>
@@ -11118,7 +11151,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>461</v>
       </c>
@@ -11132,7 +11165,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>461</v>
       </c>
@@ -11146,7 +11179,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>461</v>
       </c>
@@ -11160,7 +11193,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>528</v>
       </c>
@@ -11171,7 +11204,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>528</v>
       </c>
@@ -11182,7 +11215,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>528</v>
       </c>
@@ -11193,7 +11226,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>528</v>
       </c>
@@ -11204,7 +11237,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>528</v>
       </c>
@@ -11215,7 +11248,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>528</v>
       </c>
@@ -11226,7 +11259,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>528</v>
       </c>
@@ -11237,7 +11270,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>528</v>
       </c>
@@ -11248,7 +11281,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>528</v>
       </c>
@@ -11259,7 +11292,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>534</v>
       </c>
@@ -11270,7 +11303,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>534</v>
       </c>
@@ -11281,7 +11314,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>534</v>
       </c>
@@ -11292,7 +11325,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>534</v>
       </c>
@@ -11303,7 +11336,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>534</v>
       </c>
@@ -11314,7 +11347,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>534</v>
       </c>
@@ -11325,7 +11358,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>534</v>
       </c>
@@ -11336,7 +11369,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>534</v>
       </c>
@@ -11347,7 +11380,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" t="s">
         <v>534</v>
       </c>
@@ -11358,7 +11391,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" t="s">
         <v>467</v>
       </c>
@@ -11372,7 +11405,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" t="s">
         <v>467</v>
       </c>
@@ -11386,7 +11419,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" t="s">
         <v>557</v>
       </c>
@@ -11397,7 +11430,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" t="s">
         <v>557</v>
       </c>
@@ -11408,7 +11441,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" t="s">
         <v>565</v>
       </c>
@@ -11419,7 +11452,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" t="s">
         <v>565</v>
       </c>
@@ -11432,15 +11465,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>449</v>
       </c>
@@ -11462,15 +11496,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -11487,7 +11522,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>607</v>
       </c>
@@ -11506,15 +11541,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -11522,7 +11558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -11532,15 +11568,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -11559,15 +11596,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -11584,7 +11622,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -11598,7 +11636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -11615,7 +11653,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -11632,7 +11670,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -11649,7 +11687,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -11668,15 +11706,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -11699,630 +11738,630 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>47</v>
       </c>
       <c r="B2" t="s">
         <v>48</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>49</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>47</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>47</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>53</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>47</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="s">
         <v>55</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>47</v>
       </c>
       <c r="B6" t="s">
         <v>48</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>47</v>
       </c>
       <c r="B7" t="s">
         <v>48</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="s">
         <v>58</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>47</v>
       </c>
       <c r="B8" t="s">
         <v>48</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>47</v>
       </c>
       <c r="B9" t="s">
         <v>48</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="s">
         <v>61</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>47</v>
       </c>
       <c r="B10" t="s">
         <v>48</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="s">
         <v>63</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>2</v>
       </c>
       <c r="F10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>48</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="s">
         <v>65</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>47</v>
       </c>
       <c r="B12" t="s">
         <v>48</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="s">
         <v>66</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>47</v>
       </c>
       <c r="B13" t="s">
         <v>48</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="s">
         <v>68</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>47</v>
       </c>
       <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="s">
         <v>70</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>47</v>
       </c>
       <c r="B15" t="s">
         <v>48</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="s">
         <v>71</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>47</v>
       </c>
       <c r="B16" t="s">
         <v>48</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="s">
         <v>73</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>47</v>
       </c>
       <c r="B17" t="s">
         <v>48</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="s">
         <v>75</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>47</v>
       </c>
       <c r="B18" t="s">
         <v>48</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>3</v>
       </c>
       <c r="D18" t="s">
         <v>76</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>47</v>
       </c>
       <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="s">
         <v>78</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>2</v>
       </c>
       <c r="F19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>47</v>
       </c>
       <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="s">
         <v>80</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>47</v>
       </c>
       <c r="B21" t="s">
         <v>48</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>3</v>
       </c>
       <c r="D21" t="s">
         <v>81</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>47</v>
       </c>
       <c r="B22" t="s">
         <v>48</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="s">
         <v>83</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>47</v>
       </c>
       <c r="B23" t="s">
         <v>48</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="s">
         <v>85</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>47</v>
       </c>
       <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>3</v>
       </c>
       <c r="D24" t="s">
         <v>86</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>47</v>
       </c>
       <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>3</v>
       </c>
       <c r="D25" t="s">
         <v>88</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>2</v>
       </c>
       <c r="F25" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" t="s">
         <v>47</v>
       </c>
       <c r="B26" t="s">
         <v>48</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>2</v>
       </c>
       <c r="D26" t="s">
         <v>90</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" t="s">
         <v>47</v>
       </c>
       <c r="B27" t="s">
         <v>48</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>3</v>
       </c>
       <c r="D27" t="s">
         <v>91</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" t="s">
         <v>47</v>
       </c>
       <c r="B28" t="s">
         <v>48</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="s">
         <v>93</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>2</v>
       </c>
       <c r="F28" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" t="s">
         <v>47</v>
       </c>
       <c r="B29" t="s">
         <v>48</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>2</v>
       </c>
       <c r="D29" t="s">
         <v>95</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" t="s">
         <v>47</v>
       </c>
       <c r="B30" t="s">
         <v>48</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>3</v>
       </c>
       <c r="D30" t="s">
         <v>96</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" t="s">
         <v>47</v>
       </c>
       <c r="B31" t="s">
         <v>48</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>3</v>
       </c>
       <c r="D31" t="s">
         <v>98</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" t="s">
         <v>47</v>
       </c>
       <c r="B32" t="s">
         <v>48</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>2</v>
       </c>
       <c r="D32" t="s">
         <v>100</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33" t="s">
         <v>47</v>
       </c>
       <c r="B33" t="s">
         <v>48</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>3</v>
       </c>
       <c r="D33" t="s">
         <v>101</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34" t="s">
         <v>47</v>
       </c>
       <c r="B34" t="s">
         <v>48</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="s">
         <v>103</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>2</v>
       </c>
       <c r="F34" t="s">
@@ -12331,15 +12370,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -12362,20 +12402,20 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>109</v>
       </c>
       <c r="B2" t="s">
         <v>110</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>49</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="s">
@@ -12384,15 +12424,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>111</v>
       </c>
@@ -12406,7 +12447,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -12420,7 +12461,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>115</v>
       </c>
@@ -12434,7 +12475,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>115</v>
       </c>
@@ -12450,15 +12491,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -12484,11 +12526,11 @@
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>50</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -12503,5 +12545,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/inst/extdata/exampleARS_3.xlsx
+++ b/inst/extdata/exampleARS_3.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="622">
   <si>
     <t>generatedUsing</t>
   </si>
@@ -1952,6 +1952,15 @@
   <si>
     <t xml:space="preserve">Mth_02_02_%_DEN</t>
   </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
 </sst>
 </file>
 
@@ -1970,7 +1979,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <b/>
     </font>
     <font>
@@ -1982,8 +1990,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <strike/>
     </font>
   </fonts>
@@ -5058,7 +5064,7 @@
         <v>234</v>
       </c>
       <c r="P2" t="s">
-        <v>309</v>
+        <v>619</v>
       </c>
     </row>
     <row r="3">
@@ -5099,7 +5105,7 @@
         <v>234</v>
       </c>
       <c r="P3" t="s">
-        <v>312</v>
+        <v>620</v>
       </c>
     </row>
     <row r="4">
@@ -5140,7 +5146,7 @@
         <v>234</v>
       </c>
       <c r="P4" t="s">
-        <v>315</v>
+        <v>621</v>
       </c>
     </row>
     <row r="5">
@@ -6121,7 +6127,7 @@
         <v>234</v>
       </c>
       <c r="P25" t="s">
-        <v>309</v>
+        <v>619</v>
       </c>
     </row>
     <row r="26">
@@ -6162,7 +6168,7 @@
         <v>234</v>
       </c>
       <c r="P26" t="s">
-        <v>312</v>
+        <v>620</v>
       </c>
     </row>
     <row r="27">
@@ -6203,7 +6209,7 @@
         <v>234</v>
       </c>
       <c r="P27" t="s">
-        <v>315</v>
+        <v>621</v>
       </c>
     </row>
     <row r="28">
@@ -6954,7 +6960,7 @@
         <v>234</v>
       </c>
       <c r="P44" t="s">
-        <v>309</v>
+        <v>619</v>
       </c>
     </row>
     <row r="45">
@@ -6995,7 +7001,7 @@
         <v>234</v>
       </c>
       <c r="P45" t="s">
-        <v>312</v>
+        <v>620</v>
       </c>
     </row>
     <row r="46">
@@ -7036,7 +7042,7 @@
         <v>234</v>
       </c>
       <c r="P46" t="s">
-        <v>315</v>
+        <v>621</v>
       </c>
     </row>
     <row r="47">
@@ -7602,7 +7608,7 @@
         <v>234</v>
       </c>
       <c r="P59" t="s">
-        <v>309</v>
+        <v>619</v>
       </c>
     </row>
     <row r="60">
@@ -7643,7 +7649,7 @@
         <v>234</v>
       </c>
       <c r="P60" t="s">
-        <v>312</v>
+        <v>620</v>
       </c>
     </row>
     <row r="61">
@@ -7684,7 +7690,7 @@
         <v>234</v>
       </c>
       <c r="P61" t="s">
-        <v>315</v>
+        <v>621</v>
       </c>
     </row>
     <row r="62">
@@ -8250,7 +8256,7 @@
         <v>234</v>
       </c>
       <c r="P74" t="s">
-        <v>309</v>
+        <v>619</v>
       </c>
     </row>
     <row r="75">
@@ -8291,7 +8297,7 @@
         <v>234</v>
       </c>
       <c r="P75" t="s">
-        <v>312</v>
+        <v>620</v>
       </c>
     </row>
     <row r="76">
@@ -8332,7 +8338,7 @@
         <v>234</v>
       </c>
       <c r="P76" t="s">
-        <v>315</v>
+        <v>621</v>
       </c>
     </row>
     <row r="77">

--- a/inst/extdata/exampleARS_3.xlsx
+++ b/inst/extdata/exampleARS_3.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="641">
   <si>
     <t>generatedUsing</t>
   </si>
@@ -1960,6 +1960,63 @@
   </si>
   <si>
     <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERSEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RACE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMERICAN INDIAN OR ALASKA NATIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASIAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLACK OR AFRICAN AMERICAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATIVE HAWAIIAN OR OTHER PACIFIC ISLANDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHITE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTHER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT REPORTED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNKNOWN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETHNIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HISPANIC OR LATINO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT HISPANIC OR LATINO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COUNTRY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
   </si>
 </sst>
 </file>
@@ -5163,7 +5220,7 @@
         <v>225</v>
       </c>
       <c r="E5" t="s">
-        <v>319</v>
+        <v>622</v>
       </c>
       <c r="F5" t="s">
         <v>306</v>
@@ -5187,13 +5244,13 @@
         <v>225</v>
       </c>
       <c r="N5" t="s">
-        <v>319</v>
+        <v>622</v>
       </c>
       <c r="O5" t="s">
         <v>234</v>
       </c>
       <c r="P5" t="s">
-        <v>321</v>
+        <v>623</v>
       </c>
     </row>
     <row r="6">
@@ -5210,7 +5267,7 @@
         <v>225</v>
       </c>
       <c r="E6" t="s">
-        <v>319</v>
+        <v>622</v>
       </c>
       <c r="F6" t="s">
         <v>306</v>
@@ -5234,13 +5291,13 @@
         <v>225</v>
       </c>
       <c r="N6" t="s">
-        <v>319</v>
+        <v>622</v>
       </c>
       <c r="O6" t="s">
         <v>234</v>
       </c>
       <c r="P6" t="s">
-        <v>323</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7">
@@ -5257,7 +5314,7 @@
         <v>225</v>
       </c>
       <c r="E7" t="s">
-        <v>319</v>
+        <v>622</v>
       </c>
       <c r="F7" t="s">
         <v>306</v>
@@ -5281,13 +5338,13 @@
         <v>225</v>
       </c>
       <c r="N7" t="s">
-        <v>319</v>
+        <v>622</v>
       </c>
       <c r="O7" t="s">
         <v>234</v>
       </c>
       <c r="P7" t="s">
-        <v>325</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5304,7 +5361,7 @@
         <v>225</v>
       </c>
       <c r="E8" t="s">
-        <v>319</v>
+        <v>622</v>
       </c>
       <c r="F8" t="s">
         <v>306</v>
@@ -5328,13 +5385,13 @@
         <v>225</v>
       </c>
       <c r="N8" t="s">
-        <v>319</v>
+        <v>622</v>
       </c>
       <c r="O8" t="s">
         <v>234</v>
       </c>
       <c r="P8" t="s">
-        <v>327</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9">
@@ -5492,7 +5549,7 @@
         <v>225</v>
       </c>
       <c r="E12" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="F12" t="s">
         <v>306</v>
@@ -5516,13 +5573,13 @@
         <v>225</v>
       </c>
       <c r="N12" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="O12" t="s">
         <v>234</v>
       </c>
       <c r="P12" t="s">
-        <v>344</v>
+        <v>628</v>
       </c>
     </row>
     <row r="13">
@@ -5539,7 +5596,7 @@
         <v>225</v>
       </c>
       <c r="E13" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="F13" t="s">
         <v>306</v>
@@ -5563,13 +5620,13 @@
         <v>225</v>
       </c>
       <c r="N13" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="O13" t="s">
         <v>234</v>
       </c>
       <c r="P13" t="s">
-        <v>346</v>
+        <v>629</v>
       </c>
     </row>
     <row r="14">
@@ -5586,7 +5643,7 @@
         <v>225</v>
       </c>
       <c r="E14" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="F14" t="s">
         <v>306</v>
@@ -5610,13 +5667,13 @@
         <v>225</v>
       </c>
       <c r="N14" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="O14" t="s">
         <v>234</v>
       </c>
       <c r="P14" t="s">
-        <v>348</v>
+        <v>630</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5690,7 @@
         <v>225</v>
       </c>
       <c r="E15" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="F15" t="s">
         <v>306</v>
@@ -5657,13 +5714,13 @@
         <v>225</v>
       </c>
       <c r="N15" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="O15" t="s">
         <v>234</v>
       </c>
       <c r="P15" t="s">
-        <v>350</v>
+        <v>631</v>
       </c>
     </row>
     <row r="16">
@@ -5680,7 +5737,7 @@
         <v>225</v>
       </c>
       <c r="E16" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="F16" t="s">
         <v>306</v>
@@ -5704,13 +5761,13 @@
         <v>225</v>
       </c>
       <c r="N16" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="O16" t="s">
         <v>234</v>
       </c>
       <c r="P16" t="s">
-        <v>352</v>
+        <v>632</v>
       </c>
     </row>
     <row r="17">
@@ -5727,7 +5784,7 @@
         <v>225</v>
       </c>
       <c r="E17" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="F17" t="s">
         <v>306</v>
@@ -5751,13 +5808,13 @@
         <v>225</v>
       </c>
       <c r="N17" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="O17" t="s">
         <v>234</v>
       </c>
       <c r="P17" t="s">
-        <v>354</v>
+        <v>633</v>
       </c>
     </row>
     <row r="18">
@@ -5774,7 +5831,7 @@
         <v>225</v>
       </c>
       <c r="E18" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="F18" t="s">
         <v>306</v>
@@ -5798,13 +5855,13 @@
         <v>225</v>
       </c>
       <c r="N18" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="O18" t="s">
         <v>234</v>
       </c>
       <c r="P18" t="s">
-        <v>356</v>
+        <v>634</v>
       </c>
     </row>
     <row r="19">
@@ -5821,7 +5878,7 @@
         <v>225</v>
       </c>
       <c r="E19" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="F19" t="s">
         <v>306</v>
@@ -5845,13 +5902,13 @@
         <v>225</v>
       </c>
       <c r="N19" t="s">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="O19" t="s">
         <v>234</v>
       </c>
       <c r="P19" t="s">
-        <v>327</v>
+        <v>635</v>
       </c>
     </row>
     <row r="20">
@@ -5868,7 +5925,7 @@
         <v>225</v>
       </c>
       <c r="E20" t="s">
-        <v>361</v>
+        <v>636</v>
       </c>
       <c r="F20" t="s">
         <v>306</v>
@@ -5892,13 +5949,13 @@
         <v>225</v>
       </c>
       <c r="N20" t="s">
-        <v>361</v>
+        <v>636</v>
       </c>
       <c r="O20" t="s">
         <v>234</v>
       </c>
       <c r="P20" t="s">
-        <v>363</v>
+        <v>637</v>
       </c>
     </row>
     <row r="21">
@@ -5915,7 +5972,7 @@
         <v>225</v>
       </c>
       <c r="E21" t="s">
-        <v>361</v>
+        <v>636</v>
       </c>
       <c r="F21" t="s">
         <v>306</v>
@@ -5939,13 +5996,13 @@
         <v>225</v>
       </c>
       <c r="N21" t="s">
-        <v>361</v>
+        <v>636</v>
       </c>
       <c r="O21" t="s">
         <v>234</v>
       </c>
       <c r="P21" t="s">
-        <v>365</v>
+        <v>638</v>
       </c>
     </row>
     <row r="22">
@@ -5962,7 +6019,7 @@
         <v>225</v>
       </c>
       <c r="E22" t="s">
-        <v>361</v>
+        <v>636</v>
       </c>
       <c r="F22" t="s">
         <v>306</v>
@@ -5986,13 +6043,13 @@
         <v>225</v>
       </c>
       <c r="N22" t="s">
-        <v>361</v>
+        <v>636</v>
       </c>
       <c r="O22" t="s">
         <v>234</v>
       </c>
       <c r="P22" t="s">
-        <v>356</v>
+        <v>634</v>
       </c>
     </row>
     <row r="23">
@@ -6009,7 +6066,7 @@
         <v>225</v>
       </c>
       <c r="E23" t="s">
-        <v>361</v>
+        <v>636</v>
       </c>
       <c r="F23" t="s">
         <v>306</v>
@@ -6033,13 +6090,13 @@
         <v>225</v>
       </c>
       <c r="N23" t="s">
-        <v>361</v>
+        <v>636</v>
       </c>
       <c r="O23" t="s">
         <v>234</v>
       </c>
       <c r="P23" t="s">
-        <v>327</v>
+        <v>635</v>
       </c>
     </row>
     <row r="24">
@@ -6056,7 +6113,7 @@
         <v>225</v>
       </c>
       <c r="E24" t="s">
-        <v>371</v>
+        <v>639</v>
       </c>
       <c r="F24" t="s">
         <v>306</v>
@@ -6080,13 +6137,13 @@
         <v>225</v>
       </c>
       <c r="N24" t="s">
-        <v>371</v>
+        <v>639</v>
       </c>
       <c r="O24" t="s">
         <v>234</v>
       </c>
       <c r="P24" t="s">
-        <v>373</v>
+        <v>640</v>
       </c>
     </row>
     <row r="25">
